--- a/docs/단어 리스트 추가 및 수정내용.xlsx
+++ b/docs/단어 리스트 추가 및 수정내용.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4406" uniqueCount="1246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4406" uniqueCount="1247">
   <si>
     <t>대분류</t>
   </si>
@@ -3762,6 +3762,9 @@
   </si>
   <si>
     <t>피곤한</t>
+  </si>
+  <si>
+    <t>모자, 야구모자</t>
   </si>
 </sst>
 </file>
@@ -15413,7 +15416,7 @@
         <v>950</v>
       </c>
       <c r="D386" s="23" t="s">
-        <v>951</v>
+        <v>1246</v>
       </c>
       <c r="E386" s="24" t="s">
         <v>952</v>
